--- a/output/2026年4月/党费收缴子表/2026年4月-中共新疆大学计算机科学与技术学院本科生第四支部委员会-党费收缴子表.xlsx
+++ b/output/2026年4月/党费收缴子表/2026年4月-中共新疆大学计算机科学与技术学院本科生第四支部委员会-党费收缴子表.xlsx
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0</v>
+        <v>1125</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0</v>
@@ -620,10 +620,10 @@
         <v>0</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0</v>
+        <v>1125</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="5">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0</v>
+        <v>1126</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>0</v>
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0</v>
+        <v>1126</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="6">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>1127</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>0</v>
@@ -718,10 +718,10 @@
         <v>0</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0</v>
+        <v>1127</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="7">
@@ -744,15 +744,15 @@
       <c r="M7" s="8" t="n"/>
       <c r="N7" s="8" t="n"/>
       <c r="O7" s="3" t="n">
-        <v>0</v>
+        <v>16.8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A7:N7"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="G2:N2"/>
-    <mergeCell ref="A7:N7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
